--- a/data/trans_orig/P6706-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6706-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25366</t>
+          <t>25906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>50628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13688</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>32764</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43144</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>74219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49976</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>41747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>71721</t>
+          <t>72075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>42650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71046</t>
+          <t>69245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,82 +973,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>42244</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>31759</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>54911</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>22,21%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>28,87%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>97849</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>80820</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>115961</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>16,46%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>23,61%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42244</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30996</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>55487</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>16,3%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>97849</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>80865</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>117311</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>19,92%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>16,47%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53463</t>
+          <t>55162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83379</t>
+          <t>84633</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>22071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83759</t>
+          <t>82888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119662</t>
+          <t>118959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87017</t>
+          <t>88048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>122715</t>
+          <t>122549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62233</t>
+          <t>63272</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91349</t>
+          <t>91878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161525</t>
+          <t>157594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204885</t>
+          <t>201765</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22032</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45924</t>
+          <t>45682</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12360</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38160</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67207</t>
+          <t>68003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28139</t>
+          <t>28379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26151</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50236</t>
+          <t>51175</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59332</t>
+          <t>58999</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30705</t>
+          <t>29753</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55489</t>
+          <t>54229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69998</t>
+          <t>69554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105187</t>
+          <t>106633</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62831</t>
+          <t>63774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94584</t>
+          <t>94840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>24186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45931</t>
+          <t>46088</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96564</t>
+          <t>93631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136179</t>
+          <t>133105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64577</t>
+          <t>63847</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94711</t>
+          <t>97131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>41055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67677</t>
+          <t>66898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112074</t>
+          <t>112929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150944</t>
+          <t>153454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>49496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78653</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13548</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68718</t>
+          <t>67921</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101813</t>
+          <t>98442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>26581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>48974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65953</t>
+          <t>68720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>52047</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78921</t>
+          <t>80377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>13907</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31695</t>
+          <t>32196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>71378</t>
+          <t>71877</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105306</t>
+          <t>105349</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33352</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57026</t>
+          <t>58947</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>50966</t>
+          <t>50852</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80122</t>
+          <t>79496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52988</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81174</t>
+          <t>82096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23230</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42981</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81833</t>
+          <t>83779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115562</t>
+          <t>117994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70047</t>
+          <t>70727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103468</t>
+          <t>104142</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60872</t>
+          <t>61416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111858</t>
+          <t>112623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153733</t>
+          <t>154980</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>37520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63924</t>
+          <t>66445</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>42972</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64161</t>
+          <t>65147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>100491</t>
+          <t>99550</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64920</t>
+          <t>64567</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97766</t>
+          <t>98340</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46956</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>74611</t>
+          <t>75720</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120049</t>
+          <t>120054</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162041</t>
+          <t>162881</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65298</t>
+          <t>64885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96372</t>
+          <t>97977</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49127</t>
+          <t>48948</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78389</t>
+          <t>79408</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120129</t>
+          <t>121353</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162681</t>
+          <t>164538</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111060</t>
+          <t>111094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>150290</t>
+          <t>150176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80293</t>
+          <t>79162</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114177</t>
+          <t>112341</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>202532</t>
+          <t>201433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>252528</t>
+          <t>257438</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49857</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>59510</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>69053</t>
+          <t>69913</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102252</t>
+          <t>100869</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28657</t>
+          <t>29865</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19758</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>36883</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62784</t>
+          <t>60937</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>24564</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45867</t>
+          <t>46740</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20848</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41718</t>
+          <t>42283</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>50085</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79399</t>
+          <t>79817</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39728</t>
+          <t>40122</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>20629</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>42279</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>45467</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>74138</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>19495</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>39873</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>29570</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52694</t>
+          <t>53077</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>54088</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>84976</t>
+          <t>86091</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>229336</t>
+          <t>225761</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>288008</t>
+          <t>286664</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>132484</t>
+          <t>129673</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>180651</t>
+          <t>177216</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>371716</t>
+          <t>372392</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>443911</t>
+          <t>449590</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>138138</t>
+          <t>136972</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>187647</t>
+          <t>186011</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>92323</t>
+          <t>93048</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>135546</t>
+          <t>135161</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>243925</t>
+          <t>244044</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>305534</t>
+          <t>308004</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>249378</t>
+          <t>250177</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>314760</t>
+          <t>311762</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>170481</t>
+          <t>170042</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>224921</t>
+          <t>221584</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>437739</t>
+          <t>439168</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>521130</t>
+          <t>519210</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>268148</t>
+          <t>268667</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>333994</t>
+          <t>331125</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>156088</t>
+          <t>154371</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>206083</t>
+          <t>202943</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>441441</t>
+          <t>440557</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>521942</t>
+          <t>520142</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>373341</t>
+          <t>373216</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>445488</t>
+          <t>444261</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>270177</t>
+          <t>268724</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>330129</t>
+          <t>327760</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>665191</t>
+          <t>665428</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>760057</t>
+          <t>755784</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34888</t>
+          <t>35062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61060</t>
+          <t>61700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52529</t>
+          <t>52116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84819</t>
+          <t>82300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>49203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16668</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34959</t>
+          <t>34335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49484</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77845</t>
+          <t>78567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>49203</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80210</t>
+          <t>79864</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41955</t>
+          <t>41426</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68830</t>
+          <t>66919</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98005</t>
+          <t>96209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>136893</t>
+          <t>137581</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37036</t>
+          <t>35615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>62956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32872</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56182</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>74850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111096</t>
+          <t>112987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65840</t>
+          <t>67137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>97052</t>
+          <t>98848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58861</t>
+          <t>58704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86147</t>
+          <t>86539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133827</t>
+          <t>134600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175383</t>
+          <t>175833</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53378</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>24255</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47591</t>
+          <t>45938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59652</t>
+          <t>59072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90753</t>
+          <t>92115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>22829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>23456</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44921</t>
+          <t>43590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52293</t>
+          <t>51547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82767</t>
+          <t>81538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39989</t>
+          <t>39490</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67660</t>
+          <t>66663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57133</t>
+          <t>56440</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78545</t>
+          <t>78875</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>113827</t>
+          <t>113285</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41298</t>
+          <t>42138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67489</t>
+          <t>69475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>43580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70272</t>
+          <t>69062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103972</t>
+          <t>103671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51065</t>
+          <t>51129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>80063</t>
+          <t>80537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36385</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61567</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93165</t>
+          <t>92068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132184</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50608</t>
+          <t>52597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>62390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>32191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>56354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37255</t>
+          <t>37526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64366</t>
+          <t>64716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37734</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62241</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31223</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57635</t>
+          <t>57081</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86556</t>
+          <t>86914</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43709</t>
+          <t>43445</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68863</t>
+          <t>68841</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54295</t>
+          <t>52826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81900</t>
+          <t>83047</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22286</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36623</t>
+          <t>36330</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61880</t>
+          <t>61718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98581</t>
+          <t>99115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136347</t>
+          <t>138590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30036</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54258</t>
+          <t>55419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>134910</t>
+          <t>136867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182492</t>
+          <t>182520</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>60304</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94848</t>
+          <t>91950</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>35040</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60570</t>
+          <t>63189</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>104070</t>
+          <t>104806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>146510</t>
+          <t>147887</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83678</t>
+          <t>86298</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121476</t>
+          <t>122537</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>68347</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101281</t>
+          <t>102535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>162025</t>
+          <t>163690</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>212097</t>
+          <t>213810</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>89880</t>
+          <t>89199</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>126155</t>
+          <t>125776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58509</t>
+          <t>58212</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89409</t>
+          <t>88049</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157171</t>
+          <t>155698</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205465</t>
+          <t>202166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68637</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>104199</t>
+          <t>101113</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>107784</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>144188</t>
+          <t>142579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>183322</t>
+          <t>183149</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>234293</t>
+          <t>233185</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>50894</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>76692</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45106</t>
+          <t>43970</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>70099</t>
+          <t>69719</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99939</t>
+          <t>101844</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>137988</t>
+          <t>138309</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26649</t>
+          <t>26317</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48607</t>
+          <t>49819</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>33467</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>57055</t>
+          <t>57021</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>65746</t>
+          <t>65866</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>99809</t>
+          <t>98463</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>30206</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52281</t>
+          <t>53039</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>30373</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>65493</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>99534</t>
+          <t>99269</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43746</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>25953</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>47228</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53435</t>
+          <t>52901</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>84716</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30730</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>29843</t>
+          <t>30707</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>55177</t>
+          <t>56419</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>274410</t>
+          <t>272189</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>336913</t>
+          <t>335194</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>138138</t>
+          <t>139542</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>186704</t>
+          <t>186387</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>429595</t>
+          <t>431821</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>508737</t>
+          <t>507843</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>201751</t>
+          <t>202246</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>259851</t>
+          <t>258010</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>133048</t>
+          <t>133171</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>176750</t>
+          <t>180122</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>347886</t>
+          <t>350756</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>422188</t>
+          <t>424292</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>277351</t>
+          <t>276765</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>341101</t>
+          <t>341040</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>219600</t>
+          <t>217807</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>274939</t>
+          <t>271939</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>509988</t>
+          <t>513828</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>597274</t>
+          <t>591446</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>263615</t>
+          <t>268521</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>327968</t>
+          <t>331374</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>169328</t>
+          <t>171617</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>219859</t>
+          <t>223742</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>452960</t>
+          <t>452991</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>535520</t>
+          <t>532329</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>255223</t>
+          <t>254809</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>318256</t>
+          <t>317973</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>252299</t>
+          <t>253948</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>312249</t>
+          <t>312345</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>526717</t>
+          <t>521443</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>609717</t>
+          <t>605789</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26330</t>
+          <t>27725</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,32 +9412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29110</t>
+          <t>30880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>47839</t>
+          <t>50608</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37205</t>
+          <t>38823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59434</t>
+          <t>64097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -9490,32 +9490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9525,32 +9525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>33828</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,32 +9638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20864</t>
+          <t>22224</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>15633</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9673,32 +9673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36744</t>
+          <t>44025</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27623</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47906</t>
+          <t>57091</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>13198</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25296</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -9829,32 +9829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14368</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25224</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>40708</t>
+          <t>43497</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>57161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>85968</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>85968</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80927</t>
+          <t>85968</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>169925</t>
+          <t>185974</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>169925</t>
+          <t>185974</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>169925</t>
+          <t>185974</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21269</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>15380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30131</t>
+          <t>32042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17981</t>
+          <t>20498</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24921</t>
+          <t>28241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>43435</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30123</t>
+          <t>33954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50477</t>
+          <t>55778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -10172,32 +10172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>10026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>24913</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>35019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>27178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>33447</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23536</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42832</t>
+          <t>43558</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14973</t>
+          <t>15001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26818</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>17711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,27 +10581,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>31068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>129992</t>
+          <t>140471</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>129992</t>
+          <t>140471</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>129992</t>
+          <t>140471</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,32 +10741,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21831</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118497</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,32 +10776,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,32 +10811,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25105</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102732</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>37,2%</t>
         </is>
       </c>
     </row>
@@ -10854,32 +10854,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>15259</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73714</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10889,32 +10889,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>10678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65970</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12273</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68971</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,32 +11002,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7832</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>20192</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79833</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>252942</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>297947</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12375</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>258680</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43529</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>316681</t>
+          <t>27326</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60115</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72387</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,32 +11423,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>38473</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25894</t>
+          <t>27179</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48873</t>
+          <t>52190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11493,32 +11493,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>50596</t>
+          <t>54279</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39261</t>
+          <t>41545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66119</t>
+          <t>69803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>23368</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>35446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>10991</t>
+          <t>14143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>28468</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>38625</t>
+          <t>43466</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28485</t>
+          <t>32878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>58615</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -11649,17 +11649,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35302</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47068</t>
+          <t>51177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36996</t>
+          <t>41876</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>64055</t>
+          <t>70161</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77602</t>
+          <t>86399</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>28485</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>34060</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>27524</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47114</t>
+          <t>51212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22538</t>
+          <t>26790</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>21294</t>
+          <t>21926</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>39700</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>46007</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>34902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53560</t>
+          <t>60389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>105592</t>
+          <t>117613</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>105592</t>
+          <t>117613</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105592</t>
+          <t>117613</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>229333</t>
+          <t>252076</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>229333</t>
+          <t>252076</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>229333</t>
+          <t>252076</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,32 +12105,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>43462</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42393</t>
+          <t>56235</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,32 +12140,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12175,32 +12175,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>53142</t>
+          <t>68307</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40704</t>
+          <t>54007</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67226</t>
+          <t>84062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14797</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24383</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>20599</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>28374</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22326</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41564</t>
+          <t>49029</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12331,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,32 +12366,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15197</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>31122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>38759</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2613</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13051</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>30289</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,67 +12592,67 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>19,05%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>17020</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>8776</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>31053</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>4,81%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>15036</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>8415</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>27042</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>137831</t>
+          <t>155361</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>50021</t>
+          <t>132175</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>229667</t>
+          <t>181257</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>78100</t>
+          <t>87463</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>65226</t>
+          <t>71700</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>90605</t>
+          <t>103051</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>215931</t>
+          <t>242824</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>94829</t>
+          <t>217237</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>291947</t>
+          <t>273633</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>73471</t>
+          <t>82740</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>29010</t>
+          <t>65466</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>124771</t>
+          <t>102320</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>52004</t>
+          <t>61437</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>41212</t>
+          <t>50011</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>64550</t>
+          <t>75929</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>125475</t>
+          <t>144176</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>56543</t>
+          <t>123494</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>175648</t>
+          <t>170748</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>94003</t>
+          <t>105469</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>36262</t>
+          <t>87164</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>159240</t>
+          <t>128921</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>93179</t>
+          <t>101115</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>78757</t>
+          <t>85807</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>108694</t>
+          <t>117211</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>187182</t>
+          <t>206585</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>96312</t>
+          <t>181955</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>254752</t>
+          <t>231157</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>295382</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>74417</t>
+          <t>44989</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>518665</t>
+          <t>77000</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>53622</t>
+          <t>61438</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>43610</t>
+          <t>49386</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>68578</t>
+          <t>79167</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>349004</t>
+          <t>120976</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>131818</t>
+          <t>101625</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>704448</t>
+          <t>141823</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>69581</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>50643</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>106533</t>
+          <t>92097</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>71140</t>
+          <t>76564</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>58092</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>84924</t>
+          <t>91184</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>133645</t>
+          <t>146145</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>61337</t>
+          <t>122357</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>186246</t>
+          <t>171867</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>663192</t>
+          <t>472688</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>663192</t>
+          <t>472688</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>663192</t>
+          <t>472688</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>348044</t>
+          <t>388017</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>348044</t>
+          <t>388017</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>348044</t>
+          <t>388017</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1011236</t>
+          <t>860705</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1011236</t>
+          <t>860705</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1011236</t>
+          <t>860705</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
